--- a/output/LK-000148_202606.xlsx
+++ b/output/LK-000148_202606.xlsx
@@ -73482,47 +73482,47 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080391</t>
+          <t>JIYBBS106990</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080391</t>
+          <t>JIYBBS106990</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>AGA080391</t>
+          <t>BBS106990</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LAVENDER  /1L</t>
+          <t>BABY SOFT   /410ML</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080491</t>
+          <t>JIYHSR222594</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080491</t>
+          <t>JIYHSR222594</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AGA080491</t>
+          <t>HSR222594</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LAVENDER  /2L</t>
+          <t>YURI HAND SOAP LEMON  /3,7LT</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -73532,122 +73532,122 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080591</t>
+          <t>JIYMAT211191</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080591</t>
+          <t>JIYMAT211191</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>AGA080591</t>
+          <t>MAT211191</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LAVENDER  /3,7LT</t>
+          <t>YURIMATIC TOUGH STAIN  /80ML</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080791</t>
+          <t>JIYAGA080391</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080791</t>
+          <t>JIYAGA080391</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AGA080791</t>
+          <t>AGA080391</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LAVENDER  /20L</t>
+          <t>AGANOL LAVENDER  /1L</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080991</t>
+          <t>JIYAGA080491</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080991</t>
+          <t>JIYAGA080491</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>AGA080991</t>
+          <t>AGA080491</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LAVENDER  /630ML</t>
+          <t>AGANOL LAVENDER  /2L</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080991-Z0</t>
+          <t>JIYAGA080591</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080991-Z0</t>
+          <t>JIYAGA080591</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AGA080991-Z01</t>
+          <t>AGA080591</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LAVENDER /600ML + BUY 1 GET 1</t>
+          <t>AGANOL LAVENDER  /3,7LT</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080991A</t>
+          <t>JIYAGA080791</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA080991A</t>
+          <t>JIYAGA080791</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>AGA080991A</t>
+          <t>AGA080791</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LAVENDER  /630ML</t>
+          <t>AGANOL LAVENDER  /20L</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -73657,322 +73657,322 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101391A</t>
+          <t>JIYAGA080991</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101391A</t>
+          <t>JIYAGA080991</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AGA101391A</t>
+          <t>AGA080991</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>AGANOL FLORAL  /1L</t>
+          <t>AGANOL LAVENDER  /630ML</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101392</t>
+          <t>JIYAGA080991-Z0</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101392</t>
+          <t>JIYAGA080991-Z0</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>AGA101392</t>
+          <t>AGA080991-Z01</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LEMON FRESH  /1L</t>
+          <t>AGANOL LAVENDER /600ML + BUY 1 GET 1</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101393</t>
+          <t>JIYAGA080991A</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101393</t>
+          <t>JIYAGA080991A</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>AGA101393</t>
+          <t>AGA080991A</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>AGANOL MORNING FRESH W/ LEMONGRASS  /1L</t>
+          <t>AGANOL LAVENDER  /630ML</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101491A</t>
+          <t>JIYAGA101391A</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101491A</t>
+          <t>JIYAGA101391A</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>AGA101491A</t>
+          <t>AGA101391A</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>AGANOL FLORAL  /2L</t>
+          <t>AGANOL FLORAL  /1L</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101492</t>
+          <t>JIYAGA101392</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101492</t>
+          <t>JIYAGA101392</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>AGA101492</t>
+          <t>AGA101392</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LEMON FRESH  /2L</t>
+          <t>AGANOL LEMON FRESH  /1L</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101493</t>
+          <t>JIYAGA101393</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101493</t>
+          <t>JIYAGA101393</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>AGA101493</t>
+          <t>AGA101393</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>AGANOL MORNING FRESH W/ LEMONGRASS  /2L</t>
+          <t>AGANOL MORNING FRESH W/ LEMONGRASS  /1L</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101591</t>
+          <t>JIYAGA101491A</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101591</t>
+          <t>JIYAGA101491A</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>AGA101591</t>
+          <t>AGA101491A</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>AGANOL FLORAL  /3,7LT</t>
+          <t>AGANOL FLORAL  /2L</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101592</t>
+          <t>JIYAGA101492</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101592</t>
+          <t>JIYAGA101492</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>AGA101592</t>
+          <t>AGA101492</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LEMON  /3,7LT</t>
+          <t>AGANOL LEMON FRESH  /2L</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101593</t>
+          <t>JIYAGA101493</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101593</t>
+          <t>JIYAGA101493</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>AGA101593</t>
+          <t>AGA101493</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>AGANOL MORNING FRESH W/ LEMONGRASS  /3,7LT</t>
+          <t>AGANOL MORNING FRESH W/ LEMONGRASS  /2L</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101793</t>
+          <t>JIYAGA101591</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101793</t>
+          <t>JIYAGA101591</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>AGA101793</t>
+          <t>AGA101591</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>AGANOL MORNING FRESH W/ LEMONGRASS  /20L</t>
+          <t>AGANOL FLORAL  /3,7LT</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101991A</t>
+          <t>JIYAGA101592</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101991A</t>
+          <t>JIYAGA101592</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>AGA101991A</t>
+          <t>AGA101592</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>AGANOL FLORAL  /630ML</t>
+          <t>AGANOL LEMON  /3,7LT</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101991B</t>
+          <t>JIYAGA101593</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101991B</t>
+          <t>JIYAGA101593</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>AGA101991B</t>
+          <t>AGA101593</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>AGANOL FLORAL  /630ML</t>
+          <t>AGANOL MORNING FRESH W/ LEMONGRASS  /3,7LT</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101991B-Z</t>
+          <t>JIYAGA101793</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101991B-Z</t>
+          <t>JIYAGA101793</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>AGA101991B-Z01</t>
+          <t>AGA101793</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>AGANOL FLORAL /600ML + BUY 1 GET 1</t>
+          <t>AGANOL MORNING FRESH W/ LEMONGRASS  /20L</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
@@ -73982,72 +73982,72 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101992</t>
+          <t>JIYAGA101991A</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101992</t>
+          <t>JIYAGA101991A</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>AGA101992</t>
+          <t>AGA101991A</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LEMON  /630ML</t>
+          <t>AGANOL FLORAL  /630ML</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101992-Z0</t>
+          <t>JIYAGA101991B</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101992-Z0</t>
+          <t>JIYAGA101991B</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>AGA101992-Z01</t>
+          <t>AGA101991B</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LEMON /600ML + BUY 1 GET 1</t>
+          <t>AGANOL FLORAL  /630ML</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101992A</t>
+          <t>JIYAGA101991B-Z</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101992A</t>
+          <t>JIYAGA101991B-Z</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>AGA101992A</t>
+          <t>AGA101991B-Z01</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>AGANOL LEMON FRESH  /630ML</t>
+          <t>AGANOL FLORAL /600ML + BUY 1 GET 1</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
@@ -74057,47 +74057,47 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101993</t>
+          <t>JIYAGA101992</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101993</t>
+          <t>JIYAGA101992</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>AGA101993</t>
+          <t>AGA101992</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>AGANOL MORNING FRESH W/ LEMONGRASS  /630ML</t>
+          <t>AGANOL LEMON  /630ML</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101993-Z0</t>
+          <t>JIYAGA101992-Z0</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101993-Z0</t>
+          <t>JIYAGA101992-Z0</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>AGA101993-Z01</t>
+          <t>AGA101992-Z01</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>AGANOL MORNING FRESH W/ LEMONGRASS /600ML + BUY 1 GET 1</t>
+          <t>AGANOL LEMON /600ML + BUY 1 GET 1</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
@@ -74107,22 +74107,22 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101993A</t>
+          <t>JIYAGA101992A</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>JIYAGA101993A</t>
+          <t>JIYAGA101992A</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>AGA101993A</t>
+          <t>AGA101992A</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>AGANOL MORNING FRESH  /630ML</t>
+          <t>AGANOL LEMON FRESH  /630ML</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -74132,47 +74132,47 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>JIYBBS106390</t>
+          <t>JIYAGA101993</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>JIYBBS106390</t>
+          <t>JIYAGA101993</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>BBS106390</t>
+          <t>AGA101993</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>BABY SOFT   /1L</t>
+          <t>AGANOL MORNING FRESH W/ LEMONGRASS  /630ML</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>JIYBBS106590</t>
+          <t>JIYAGA101993-Z0</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>JIYBBS106590</t>
+          <t>JIYAGA101993-Z0</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>BBS106590</t>
+          <t>AGA101993-Z01</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>BABY SOFT   /3,7LT</t>
+          <t>AGANOL MORNING FRESH W/ LEMONGRASS /600ML + BUY 1 GET 1</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
@@ -74182,22 +74182,22 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>JIYBBS106990</t>
+          <t>JIYAGA101993A</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>JIYBBS106990</t>
+          <t>JIYAGA101993A</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>BBS106990</t>
+          <t>AGA101993A</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>BABY SOFT   /410ML</t>
+          <t>AGANOL MORNING FRESH  /630ML</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
@@ -74207,72 +74207,72 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>JIYBCL100280</t>
+          <t>JIYBBS106390</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>JIYBCL100280</t>
+          <t>JIYBBS106390</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>BCL100280</t>
+          <t>BBS106390</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>YURI BATHROOM CLEANER   /500ML</t>
+          <t>BABY SOFT   /1L</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>JIYBCL100390</t>
+          <t>JIYBBS106590</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>JIYBCL100390</t>
+          <t>JIYBBS106590</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>BCL100390</t>
+          <t>BBS106590</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>YURI BATHROOM CLEANER   /375ML</t>
+          <t>BABY SOFT   /3,7LT</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO112160</t>
+          <t>JIYBCL100280</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO112160</t>
+          <t>JIYBCL100280</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>BIO112160</t>
+          <t>BCL100280</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT   /250ML</t>
+          <t>YURI BATHROOM CLEANER   /500ML</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
@@ -74282,22 +74282,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO112290</t>
+          <t>JIYBCL100390</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO112290</t>
+          <t>JIYBCL100390</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>BIO112290</t>
+          <t>BCL100390</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT   /375ML</t>
+          <t>YURI BATHROOM CLEANER   /375ML</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
@@ -74307,72 +74307,72 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO112590</t>
+          <t>JIYBIO112160</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO112590</t>
+          <t>JIYBIO112160</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>BIO112590</t>
+          <t>BIO112160</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT   /3,7LT</t>
+          <t>BIOSOFT   /250ML</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO113091</t>
+          <t>JIYBIO112290</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO113091</t>
+          <t>JIYBIO112290</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>BIO113091</t>
+          <t>BIO112290</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT HIJAB DETERGENT + SOFTENER OCEAN FRESH 40ML</t>
+          <t>BIOSOFT   /375ML</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO113381</t>
+          <t>JIYBIO112590</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO113381</t>
+          <t>JIYBIO112590</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>BIO113381</t>
+          <t>BIO112590</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT HIJAB DETERGENT+SOFTENER OCEAN FRESH /900ML</t>
+          <t>BIOSOFT   /3,7LT</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
@@ -74382,22 +74382,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO113921</t>
+          <t>JIYBIO113091</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO113921</t>
+          <t>JIYBIO113091</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>BIO113921</t>
+          <t>BIO113091</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT HIJAB DETERGENT+SOFTENER OCEAN FRESH /630ML</t>
+          <t>BIOSOFT HIJAB DETERGENT + SOFTENER OCEAN FRESH 40ML</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
@@ -74407,22 +74407,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO114091</t>
+          <t>JIYBIO113381</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO114091</t>
+          <t>JIYBIO113381</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>BIO114091</t>
+          <t>BIO113381</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT HIJAB PEWANGI+SOFTENER HGR 24x10ML OCEAN FRESH</t>
+          <t>BIOSOFT HIJAB DETERGENT+SOFTENER OCEAN FRESH /900ML</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
@@ -74432,47 +74432,47 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO114391</t>
+          <t>JIYBIO113921</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO114391</t>
+          <t>JIYBIO113921</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>BIO114391</t>
+          <t>BIO113921</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT HIJAB PEWANGI+SOFTENER OCEAN FRESH /900ML</t>
+          <t>BIOSOFT HIJAB DETERGENT+SOFTENER OCEAN FRESH /630ML</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO114921</t>
+          <t>JIYBIO114091</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO114921</t>
+          <t>JIYBIO114091</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>BIO114921</t>
+          <t>BIO114091</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT HIJAB PEWANGI+SOFTENER OCEAN FRESH /630ML</t>
+          <t>BIOSOFT HIJAB PEWANGI+SOFTENER HGR 24x10ML OCEAN FRESH</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
@@ -74482,72 +74482,72 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO115281</t>
+          <t>JIYBIO114391</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO115281</t>
+          <t>JIYBIO114391</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>BIO115281</t>
+          <t>BIO114391</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT HIJAB PELICIN KAIN HALUS OCEAN FRESH SPRAY /500ML</t>
+          <t>BIOSOFT HIJAB PEWANGI+SOFTENER OCEAN FRESH /900ML</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO115291</t>
+          <t>JIYBIO114921</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO115291</t>
+          <t>JIYBIO114921</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>BIO115291</t>
+          <t>BIO114921</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT HIJAB PELICIN KAIN HALUS OCEAN FRESH /410ML</t>
+          <t>BIOSOFT HIJAB PEWANGI+SOFTENER OCEAN FRESH /630ML</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO116001</t>
+          <t>JIYBIO115281</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO116001</t>
+          <t>JIYBIO115281</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>BIO116001</t>
+          <t>BIO115281</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT HIJAB PAKET BOTOL + HADIAH</t>
+          <t>BIOSOFT HIJAB PELICIN KAIN HALUS OCEAN FRESH SPRAY /500ML</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
@@ -74557,47 +74557,47 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO116002</t>
+          <t>JIYBIO115291</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO116002</t>
+          <t>JIYBIO115291</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>BIO116002</t>
+          <t>BIO115291</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT HIJAB PAKET POUCH + HADIAH</t>
+          <t>BIOSOFT HIJAB PELICIN KAIN HALUS OCEAN FRESH /410ML</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO116261</t>
+          <t>JIYBIO116001</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>JIYBIO116261</t>
+          <t>JIYBIO116001</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>BIO116261</t>
+          <t>BIO116001</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>BIOSOFT HIJAB TRAVEL PACK</t>
+          <t>BIOSOFT HIJAB PAKET BOTOL + HADIAH</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
@@ -74607,22 +74607,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>JIYBLE123390</t>
+          <t>JIYBIO116002</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>JIYBLE123390</t>
+          <t>JIYBIO116002</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>BLE123390</t>
+          <t>BIO116002</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>YURI BLEACH MORNING FRESH  /1L</t>
+          <t>BIOSOFT HIJAB PAKET POUCH + HADIAH</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
@@ -74632,22 +74632,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>JIYBLE123392</t>
+          <t>JIYBIO116261</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>JIYBLE123392</t>
+          <t>JIYBIO116261</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>BLE123392</t>
+          <t>BIO116261</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>YURI BLEACH LEMON  /1L</t>
+          <t>BIOSOFT HIJAB TRAVEL PACK</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
@@ -74657,22 +74657,22 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>JIYBLE123590</t>
+          <t>JIYBLE123390</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>JIYBLE123590</t>
+          <t>JIYBLE123390</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>BLE123590</t>
+          <t>BLE123390</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>YURI BLEACH MORNING FRESH  /3,7LT</t>
+          <t>YURI BLEACH MORNING FRESH  /1L</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
@@ -74682,22 +74682,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>JIYBLE123592</t>
+          <t>JIYBLE123392</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>JIYBLE123592</t>
+          <t>JIYBLE123392</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>BLE123592</t>
+          <t>BLE123392</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>YURI BLEACH LEMON  /3,7LT</t>
+          <t>YURI BLEACH LEMON  /1L</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
@@ -74707,22 +74707,22 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750261</t>
+          <t>JIYBLE123590</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750261</t>
+          <t>JIYBLE123590</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>DBD750261</t>
+          <t>BLE123590</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE TOILETRIS BESAR MILK</t>
+          <t>YURI BLEACH MORNING FRESH  /3,7LT</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
@@ -74732,22 +74732,22 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750262</t>
+          <t>JIYBLE123592</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750262</t>
+          <t>JIYBLE123592</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>DBD750262</t>
+          <t>BLE123592</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE TOILETRIS BESAR HONEY</t>
+          <t>YURI BLEACH LEMON  /3,7LT</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
@@ -74757,272 +74757,272 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750291</t>
+          <t>JIYDBD750261</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750291</t>
+          <t>JIYDBD750261</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>DBD750291</t>
+          <t>DBD750261</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE BODYWASH &amp; SHAMPOO MILK /200ML</t>
+          <t>BABYDEE TOILETRIS BESAR MILK</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750292</t>
+          <t>JIYDBD750262</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750292</t>
+          <t>JIYDBD750262</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>DBD750292</t>
+          <t>DBD750262</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE BODYWASH &amp; SHAMPOO HONEY /200ML</t>
+          <t>BABYDEE TOILETRIS BESAR HONEY</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750931</t>
+          <t>JIYDBD750291</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750931</t>
+          <t>JIYDBD750291</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>DBD750931</t>
+          <t>DBD750291</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>BABY DEE BODYWASH &amp; SHAMPOO NATURAL MILK &amp; LAVENDER EXTRACT FOAMING 600ML</t>
+          <t>BABYDEE BODYWASH &amp; SHAMPOO MILK /200ML</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750931-Z0</t>
+          <t>JIYDBD750292</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750931-Z0</t>
+          <t>JIYDBD750292</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>DBD750931-Z01</t>
+          <t>DBD750292</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>BABY DEE BW&amp;SHMP NTRL MILK&amp;LVNDR EXT 600PCH+200ML</t>
+          <t>BABYDEE BODYWASH &amp; SHAMPOO HONEY /200ML</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750932</t>
+          <t>JIYDBD750931</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750932</t>
+          <t>JIYDBD750931</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>DBD750932</t>
+          <t>DBD750931</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>BABY DEE BODYWASH &amp; SHAMPOO NATURAL HONEY&amp;CHAMOMILE EXTRACT FOAMING 600ML</t>
+          <t>BABY DEE BODYWASH &amp; SHAMPOO NATURAL MILK &amp; LAVENDER EXTRACT FOAMING 600ML</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750932-Z0</t>
+          <t>JIYDBD750931-Z0</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD750932-Z0</t>
+          <t>JIYDBD750931-Z0</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>DBD750932-Z01</t>
+          <t>DBD750931-Z01</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>BABY DEE BW&amp;SHMP NTRL HNY&amp;CHAM EXT 600PCH+200ML</t>
+          <t>BABY DEE BW&amp;SHMP NTRL MILK&amp;LVNDR EXT 600PCH+200ML</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD761261</t>
+          <t>JIYDBD750932</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD761261</t>
+          <t>JIYDBD750932</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>DBD761261</t>
+          <t>DBD750932</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE TRAVEL PACK MILK</t>
+          <t>BABY DEE BODYWASH &amp; SHAMPOO NATURAL HONEY&amp;CHAMOMILE EXTRACT FOAMING 600ML</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD761262</t>
+          <t>JIYDBD750932-Z0</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD761262</t>
+          <t>JIYDBD750932-Z0</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>DBD761262</t>
+          <t>DBD750932-Z01</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE TRAVEL PACK HONEY</t>
+          <t>BABY DEE BW&amp;SHMP NTRL HNY&amp;CHAM EXT 600PCH+200ML</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD761291</t>
+          <t>JIYDBD761261</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD761291</t>
+          <t>JIYDBD761261</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>DBD761291</t>
+          <t>DBD761261</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE TALCUM MILK /200GR</t>
+          <t>BABYDEE TRAVEL PACK MILK</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD761292</t>
+          <t>JIYDBD761262</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD761292</t>
+          <t>JIYDBD761262</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>DBD761292</t>
+          <t>DBD761262</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE TALCUM HONEY /200GR</t>
+          <t>BABYDEE TRAVEL PACK HONEY</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD789091</t>
+          <t>JIYDBD761291</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD789091</t>
+          <t>JIYDBD761291</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>DBD789091</t>
+          <t>DBD761291</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE DIAPER CREAM MILK /50GR</t>
+          <t>BABYDEE TALCUM MILK /200GR</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
@@ -75032,47 +75032,47 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD789092</t>
+          <t>JIYDBD761292</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD789092</t>
+          <t>JIYDBD761292</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>DBD789092</t>
+          <t>DBD761292</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE DIAPER CREAM HONEY /50GR</t>
+          <t>BABYDEE TALCUM HONEY /200GR</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD789191</t>
+          <t>JIYDBD789091</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD789191</t>
+          <t>JIYDBD789091</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>DBD789191</t>
+          <t>DBD789091</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE DIAPER CREAM MILK /100GR</t>
+          <t>BABYDEE DIAPER CREAM MILK /50GR</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
@@ -75082,172 +75082,172 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD789192</t>
+          <t>JIYDBD789092</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD789192</t>
+          <t>JIYDBD789092</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>DBD789192</t>
+          <t>DBD789092</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE DIAPER CREAM HONEY /100GR</t>
+          <t>BABYDEE DIAPER CREAM HONEY /50GR</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794091</t>
+          <t>JIYDBD789191</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794091</t>
+          <t>JIYDBD789191</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>DBD794091</t>
+          <t>DBD789191</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE BABY LOTION MILK /50ML</t>
+          <t>BABYDEE DIAPER CREAM MILK /100GR</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794092</t>
+          <t>JIYDBD789192</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794092</t>
+          <t>JIYDBD789192</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>DBD794092</t>
+          <t>DBD789192</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE BABY LOTION HONEY /50ML</t>
+          <t>BABYDEE DIAPER CREAM HONEY /100GR</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794191</t>
+          <t>JIYDBD794091</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794191</t>
+          <t>JIYDBD794091</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>DBD794191</t>
+          <t>DBD794091</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE BABY LOTION MILK /100ML</t>
+          <t>BABYDEE BABY LOTION MILK /50ML</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794191-Z01</t>
+          <t>JIYDBD794092</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794191-Z01</t>
+          <t>JIYDBD794092</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>DBD794191-Z01</t>
+          <t>DBD794092</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>BABY-DEE LOTION NATURAL MILK &amp; LAVENDER EXTRACT 100 G BUY1 GET1 FREE</t>
+          <t>BABYDEE BABY LOTION HONEY /50ML</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794192</t>
+          <t>JIYDBD794191</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794192</t>
+          <t>JIYDBD794191</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>DBD794192</t>
+          <t>DBD794191</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>BABYDEE BABY LOTION HONEY /100ML</t>
+          <t>BABYDEE BABY LOTION MILK /100ML</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794192-Z01</t>
+          <t>JIYDBD794191-Z01</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>JIYDBD794192-Z01</t>
+          <t>JIYDBD794191-Z01</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>DBD794192-Z01</t>
+          <t>DBD794191-Z01</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>BABY-DEE LOTION NATURAL HONEY &amp; CHAMOMILE EXTRACT 100 G BUY1 GET1 FREE</t>
+          <t>BABY-DEE LOTION NATURAL MILK &amp; LAVENDER EXTRACT 100 G BUY1 GET1 FREE</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
@@ -75257,72 +75257,72 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640291</t>
+          <t>JIYDBD794192</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640291</t>
+          <t>JIYDBD794192</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>DBW640291</t>
+          <t>DBD794192</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE BODYWASH APPLE /225ML</t>
+          <t>BABYDEE BABY LOTION HONEY /100ML</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640292</t>
+          <t>JIYDBD794192-Z01</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640292</t>
+          <t>JIYDBD794192-Z01</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>DBW640292</t>
+          <t>DBD794192-Z01</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE BODYWASH GRAPE /225ML</t>
+          <t>BABY-DEE LOTION NATURAL HONEY &amp; CHAMOMILE EXTRACT 100 G BUY1 GET1 FREE</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640293</t>
+          <t>JIYDBW640291</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640293</t>
+          <t>JIYDBW640291</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>DBW640293</t>
+          <t>DBW640291</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE BODYWASH ORANGE /225ML</t>
+          <t>DEEDEE BODYWASH APPLE /225ML</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
@@ -75332,22 +75332,22 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640294</t>
+          <t>JIYDBW640292</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640294</t>
+          <t>JIYDBW640292</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>DBW640294</t>
+          <t>DBW640292</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE BODYWASH STRAWBERRY /225ML</t>
+          <t>DEEDEE BODYWASH GRAPE /225ML</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
@@ -75357,22 +75357,22 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640991</t>
+          <t>JIYDBW640293</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640991</t>
+          <t>JIYDBW640293</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>DBW640991</t>
+          <t>DBW640293</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE BODYWASH APPLE /200ML</t>
+          <t>DEEDEE BODYWASH ORANGE /225ML</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -75382,47 +75382,47 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640992</t>
+          <t>JIYDBW640294</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640992</t>
+          <t>JIYDBW640294</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>DBW640992</t>
+          <t>DBW640294</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE BODYWASH GRAPE /200ML</t>
+          <t>DEEDEE BODYWASH STRAWBERRY /225ML</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640993</t>
+          <t>JIYDBW640991</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640993</t>
+          <t>JIYDBW640991</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>DBW640993</t>
+          <t>DBW640991</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE BODYWASH ORANGE /200ML</t>
+          <t>DEEDEE BODYWASH APPLE /200ML</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -75432,47 +75432,47 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640994</t>
+          <t>JIYDBW640992</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>JIYDBW640994</t>
+          <t>JIYDBW640992</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>DBW640994</t>
+          <t>DBW640992</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE BODYWASH STRAWBERRY /200ML</t>
+          <t>DEEDEE BODYWASH GRAPE /200ML</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>JIYDDM497193</t>
+          <t>JIYDBW640993</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>JIYDDM497193</t>
+          <t>JIYDBW640993</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>DDM497193</t>
+          <t>DBW640993</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE LOT. PENOLAK NYAMUK ORANGE /50GR</t>
+          <t>DEEDEE BODYWASH ORANGE /200ML</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -75482,47 +75482,47 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>JIYDDM497194</t>
+          <t>JIYDBW640994</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>JIYDDM497194</t>
+          <t>JIYDBW640994</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>DDM497194</t>
+          <t>DBW640994</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE LOT. PENOLAK NYAMUK STRAWBERRY /50GR</t>
+          <t>DEEDEE BODYWASH STRAWBERRY /200ML</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>JIYDDM497195</t>
+          <t>JIYDDM497193</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>JIYDDM497195</t>
+          <t>JIYDDM497193</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>DDM497195</t>
+          <t>DDM497193</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE LOT. PENOLAK NYAMUK GUAVA /50GR</t>
+          <t>DEEDEE LOT. PENOLAK NYAMUK ORANGE /50GR</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
@@ -75532,22 +75532,22 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>JIYDDP356267</t>
+          <t>JIYDDM497194</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>JIYDDP356267</t>
+          <t>JIYDDM497194</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>DDP356267</t>
+          <t>DDM497194</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE PAKET</t>
+          <t>DEEDEE LOT. PENOLAK NYAMUK STRAWBERRY /50GR</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
@@ -75557,72 +75557,72 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>JIYDDP356281A</t>
+          <t>JIYDDM497195</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>JIYDDP356281A</t>
+          <t>JIYDDM497195</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>DDP356281A</t>
+          <t>DDM497195</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO (P) - APPLE BTL/250ML (POKEMON)</t>
+          <t>DEEDEE LOT. PENOLAK NYAMUK GUAVA /50GR</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>JIYDDP356282A</t>
+          <t>JIYDDP356267</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>JIYDDP356282A</t>
+          <t>JIYDDP356267</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>DDP356282A</t>
+          <t>DDP356267</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO (P) - GRAPE BTL/250ML (POKEMON)</t>
+          <t>DEEDEE PAKET</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>JIYDDP356283A</t>
+          <t>JIYDDP356281A</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>JIYDDP356283A</t>
+          <t>JIYDDP356281A</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>DDP356283A</t>
+          <t>DDP356281A</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO (P) - ORANGE BTL/250ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO (P) - APPLE BTL/250ML (POKEMON)</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -75632,97 +75632,97 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>JIYDDP356284A</t>
+          <t>JIYDDP356282A</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>JIYDDP356284A</t>
+          <t>JIYDDP356282A</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>DDP356284A</t>
+          <t>DDP356282A</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO (P) - STRAWBERRY BTL/250ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO (P) - GRAPE BTL/250ML (POKEMON)</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356191</t>
+          <t>JIYDDP356283A</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356191</t>
+          <t>JIYDDP356283A</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>DDR356191</t>
+          <t>DDP356283A</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO APPLE /45ML</t>
+          <t>DEE DEE SHAMPOO (P) - ORANGE BTL/250ML (POKEMON)</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356191A</t>
+          <t>JIYDDP356284A</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356191A</t>
+          <t>JIYDDP356284A</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>DDR356191A</t>
+          <t>DDP356284A</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO APPLE /45ML</t>
+          <t>DEE DEE SHAMPOO (P) - STRAWBERRY BTL/250ML (POKEMON)</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356192</t>
+          <t>JIYDDR356191</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356192</t>
+          <t>JIYDDR356191</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>DDR356192</t>
+          <t>DDR356191</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO GRAPE /45ML</t>
+          <t>DEEDEE SHAMPOO APPLE /45ML</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -75732,47 +75732,47 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356192A</t>
+          <t>JIYDDR356191A</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356192A</t>
+          <t>JIYDDR356191A</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>DDR356192A</t>
+          <t>DDR356191A</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO GRAPE /45ML</t>
+          <t>DEEDEE SHAMPOO APPLE /45ML</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356193</t>
+          <t>JIYDDR356192</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356193</t>
+          <t>JIYDDR356192</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>DDR356193</t>
+          <t>DDR356192</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO ORANGE /45ML</t>
+          <t>DEEDEE SHAMPOO GRAPE /45ML</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
@@ -75782,47 +75782,47 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356193A</t>
+          <t>JIYDDR356192A</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356193A</t>
+          <t>JIYDDR356192A</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>DDR356193A</t>
+          <t>DDR356192A</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO ORANGE /45ML</t>
+          <t>DEEDEE SHAMPOO GRAPE /45ML</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356194</t>
+          <t>JIYDDR356193</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356194</t>
+          <t>JIYDDR356193</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>DDR356194</t>
+          <t>DDR356193</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO STRAWBERRY /45ML</t>
+          <t>DEEDEE SHAMPOO ORANGE /45ML</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
@@ -75832,22 +75832,22 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356194A</t>
+          <t>JIYDDR356193A</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356194A</t>
+          <t>JIYDDR356193A</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>DDR356194A</t>
+          <t>DDR356193A</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO STRAWBERRY /45ML</t>
+          <t>DEEDEE SHAMPOO ORANGE /45ML</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
@@ -75857,147 +75857,147 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356291A</t>
+          <t>JIYDDR356194</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356291A</t>
+          <t>JIYDDR356194</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>DDR356291A</t>
+          <t>DDR356194</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO (RF) - APPLE BTL/250ML (POKEMON)</t>
+          <t>DEEDEE SHAMPOO STRAWBERRY /45ML</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356292A</t>
+          <t>JIYDDR356194A</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356292A</t>
+          <t>JIYDDR356194A</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>DDR356292A</t>
+          <t>DDR356194A</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO (RF) - GRAPE BTL/250ML (POKEMON)</t>
+          <t>DEEDEE SHAMPOO STRAWBERRY /45ML</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356293A</t>
+          <t>JIYDDR356291A</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356293A</t>
+          <t>JIYDDR356291A</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>DDR356293A</t>
+          <t>DDR356291A</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO (RF) - ORANGE BTL/250ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO (RF) - APPLE BTL/250ML (POKEMON)</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356294A</t>
+          <t>JIYDDR356292A</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356294A</t>
+          <t>JIYDDR356292A</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>DDR356294A</t>
+          <t>DDR356292A</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO (RF) - STRAWBERRY BTL/250ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO (RF) - GRAPE BTL/250ML (POKEMON)</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356491A</t>
+          <t>JIYDDR356293A</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356491A</t>
+          <t>JIYDDR356293A</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>DDR356491A</t>
+          <t>DDR356293A</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO - APPLE BTL/125ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO (RF) - ORANGE BTL/250ML (POKEMON)</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356492A</t>
+          <t>JIYDDR356294A</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356492A</t>
+          <t>JIYDDR356294A</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>DDR356492A</t>
+          <t>DDR356294A</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO - GRAPE BTL/125ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO (RF) - STRAWBERRY BTL/250ML (POKEMON)</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
@@ -76007,147 +76007,147 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356493A</t>
+          <t>JIYDDR356491A</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356493A</t>
+          <t>JIYDDR356491A</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>DDR356493A</t>
+          <t>DDR356491A</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO - ORANGE BTL/125ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO - APPLE BTL/125ML (POKEMON)</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356494A</t>
+          <t>JIYDDR356492A</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356494A</t>
+          <t>JIYDDR356492A</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>DDR356494A</t>
+          <t>DDR356492A</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO - STRAWBERRY BTL/125ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO - GRAPE BTL/125ML (POKEMON)</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356991A</t>
+          <t>JIYDDR356493A</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356991A</t>
+          <t>JIYDDR356493A</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>DDR356991A</t>
+          <t>DDR356493A</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO APPLE - POUCH / 200ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO - ORANGE BTL/125ML (POKEMON)</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356991A-Z0</t>
+          <t>JIYDDR356494A</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356991A-Z0</t>
+          <t>JIYDDR356494A</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>DDR356991A-Z01</t>
+          <t>DDR356494A</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO POUCH 200 ML APPLE  / BELI 1 GRATIS 1</t>
+          <t>DEE DEE SHAMPOO - STRAWBERRY BTL/125ML (POKEMON)</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356992A</t>
+          <t>JIYDDR356991A</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356992A</t>
+          <t>JIYDDR356991A</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>DDR356992A</t>
+          <t>DDR356991A</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO GRAPE - POUCH / 200ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO APPLE - POUCH / 200ML (POKEMON)</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356992A-Z0</t>
+          <t>JIYDDR356991A-Z0</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356992A-Z0</t>
+          <t>JIYDDR356991A-Z0</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>DDR356992A-Z01</t>
+          <t>DDR356991A-Z01</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO GRAPE - POUCH/200 ML BELI1 GRATIS1</t>
+          <t>DEE DEE SHAMPOO POUCH 200 ML APPLE  / BELI 1 GRATIS 1</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
@@ -76157,72 +76157,72 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356993A</t>
+          <t>JIYDDR356992A</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356993A</t>
+          <t>JIYDDR356992A</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>DDR356993A</t>
+          <t>DDR356992A</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO ORANGE - POUCH / 200ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO GRAPE - POUCH / 200ML (POKEMON)</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356993A-Z0</t>
+          <t>JIYDDR356992A-Z0</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356993A-Z0</t>
+          <t>JIYDDR356992A-Z0</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>DDR356993A-Z01</t>
+          <t>DDR356992A-Z01</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO ORANGE - POUCH/200 ML BELI1 GRATIS1</t>
+          <t>DEE DEE SHAMPOO GRAPE - POUCH/200 ML BELI1 GRATIS1</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356994A</t>
+          <t>JIYDDR356993A</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356994A</t>
+          <t>JIYDDR356993A</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>DDR356994A</t>
+          <t>DDR356993A</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO STRAWBERRY - POUCH / 200ML (POKEMON)</t>
+          <t>DEE DEE SHAMPOO ORANGE - POUCH / 200ML (POKEMON)</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
@@ -76232,72 +76232,72 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356994A-Z0</t>
+          <t>JIYDDR356993A-Z0</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>JIYDDR356994A-Z0</t>
+          <t>JIYDDR356993A-Z0</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>DDR356994A-Z01</t>
+          <t>DDR356993A-Z01</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE SHAMPOO STRAWBERRY - POUCH/200 ML BELI1 GRATIS1</t>
+          <t>DEE DEE SHAMPOO ORANGE - POUCH/200 ML BELI1 GRATIS1</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS356071</t>
+          <t>JIYDDR356994A</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS356071</t>
+          <t>JIYDDR356994A</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>DDS356071</t>
+          <t>DDR356994A</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO  APPLE /5ML</t>
+          <t>DEE DEE SHAMPOO STRAWBERRY - POUCH / 200ML (POKEMON)</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS356072</t>
+          <t>JIYDDR356994A-Z0</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS356072</t>
+          <t>JIYDDR356994A-Z0</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>DDS356072</t>
+          <t>DDR356994A-Z01</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO  GRAPE /5ML</t>
+          <t>DEE DEE SHAMPOO STRAWBERRY - POUCH/200 ML BELI1 GRATIS1</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
@@ -76307,22 +76307,22 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS356073</t>
+          <t>JIYDDS356071</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS356073</t>
+          <t>JIYDDS356071</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>DDS356073</t>
+          <t>DDS356071</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO  ORANGE /5ML</t>
+          <t>DEEDEE SHAMPOO  APPLE /5ML</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
@@ -76332,22 +76332,22 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS356074</t>
+          <t>JIYDDS356072</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS356074</t>
+          <t>JIYDDS356072</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>DDS356074</t>
+          <t>DDS356072</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO  STRAWBERRY /5ML</t>
+          <t>DEEDEE SHAMPOO  GRAPE /5ML</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
@@ -76357,122 +76357,122 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS992283A</t>
+          <t>JIYDDS356073</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS992283A</t>
+          <t>JIYDDS356073</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>DDS992283A</t>
+          <t>DDS356073</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO GREEN TEA PUMP/200ML</t>
+          <t>DEEDEE SHAMPOO  ORANGE /5ML</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS992284A</t>
+          <t>JIYDDS356074</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>JIYDDS992284A</t>
+          <t>JIYDDS356074</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>DDS992284A</t>
+          <t>DDS356074</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHAMPOO ROSE PUMP/200ML</t>
+          <t>DEEDEE SHAMPOO  STRAWBERRY /5ML</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662092</t>
+          <t>JIYDDS992283A</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662092</t>
+          <t>JIYDDS992283A</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>DFW662092</t>
+          <t>DDS992283A</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE FACIAL WASH GRAPE /100ML</t>
+          <t>DEEDEE SHAMPOO GREEN TEA PUMP/200ML</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662093</t>
+          <t>JIYDDS992284A</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662093</t>
+          <t>JIYDDS992284A</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>DFW662093</t>
+          <t>DDS992284A</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE FACIAL WASH ORANGE /100ML</t>
+          <t>DEEDEE SHAMPOO ROSE PUMP/200ML</t>
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662094</t>
+          <t>JIYDFW662092</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662094</t>
+          <t>JIYDFW662092</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>DFW662094</t>
+          <t>DFW662092</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE FACIAL WASH STRAWBERRY /100ML</t>
+          <t>DEEDEE FACIAL WASH GRAPE /100ML</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
@@ -76482,22 +76482,22 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662902</t>
+          <t>JIYDFW662093</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662902</t>
+          <t>JIYDFW662093</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>DFW662902</t>
+          <t>DFW662093</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE FACIAL WASH GRAPE /50GR</t>
+          <t>DEEDEE FACIAL WASH ORANGE /100ML</t>
         </is>
       </c>
       <c r="E122" s="3" t="n">
@@ -76507,22 +76507,22 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662903</t>
+          <t>JIYDFW662094</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662903</t>
+          <t>JIYDFW662094</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>DFW662903</t>
+          <t>DFW662094</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE FACIAL WASH ORANGE /50GR</t>
+          <t>DEEDEE FACIAL WASH STRAWBERRY /100ML</t>
         </is>
       </c>
       <c r="E123" s="3" t="n">
@@ -76532,22 +76532,22 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662904</t>
+          <t>JIYDFW662902</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>JIYDFW662904</t>
+          <t>JIYDFW662902</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>DFW662904</t>
+          <t>DFW662902</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE FACIAL WASH STRAWBERRY /50GR</t>
+          <t>DEEDEE FACIAL WASH GRAPE /50GR</t>
         </is>
       </c>
       <c r="E124" s="3" t="n">
@@ -76557,97 +76557,97 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>JIYDPK442282C</t>
+          <t>JIYDFW662903</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>JIYDPK442282C</t>
+          <t>JIYDFW662903</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>DPK442282C</t>
+          <t>DFW662903</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>DEDEE TOOTH PASTE-POKEMON GRAPE TM/50GR</t>
+          <t>DEEDEE FACIAL WASH ORANGE /50GR</t>
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>JIYDPK442283C</t>
+          <t>JIYDFW662904</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>JIYDPK442283C</t>
+          <t>JIYDFW662904</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>DPK442283C</t>
+          <t>DFW662904</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>DEDEE TOOTH PASTE-POKEMON ORANGE TM/50GR</t>
+          <t>DEEDEE FACIAL WASH STRAWBERRY /50GR</t>
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>JIYDPK442284C</t>
+          <t>JIYDPK442282C</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>JIYDPK442284C</t>
+          <t>JIYDPK442282C</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>DPK442284C</t>
+          <t>DPK442282C</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>DEDEE TOOTH PASTE-POKEMON STRAWBERRY TM/50GR</t>
+          <t>DEDEE TOOTH PASTE-POKEMON GRAPE TM/50GR</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>JIYDPS442267</t>
+          <t>JIYDPK442283C</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>JIYDPS442267</t>
+          <t>JIYDPK442283C</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>DPS442267</t>
+          <t>DPK442283C</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE T.BRUSH +T.PASTE 50GR MIX TM</t>
+          <t>DEDEE TOOTH PASTE-POKEMON ORANGE TM/50GR</t>
         </is>
       </c>
       <c r="E128" s="3" t="n">
@@ -76657,72 +76657,72 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>JIYDPT464267</t>
+          <t>JIYDPK442284C</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>JIYDPT464267</t>
+          <t>JIYDPK442284C</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>DPT464267</t>
+          <t>DPK442284C</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE TRAVEL PACK MIX</t>
+          <t>DEDEE TOOTH PASTE-POKEMON STRAWBERRY TM/50GR</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>JIYDPT464267-Z0</t>
+          <t>JIYDPS442267</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>JIYDPT464267-Z0</t>
+          <t>JIYDPS442267</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>DPT464267-Z01</t>
+          <t>DPS442267</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>DEE-DEE TRAVEL PACK MIX+FREE GIFT-DPT464267Z0</t>
+          <t>DEEDEE T.BRUSH +T.PASTE 50GR MIX TM</t>
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650264</t>
+          <t>JIYDPT464267</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650264</t>
+          <t>JIYDPT464267</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>DSC650264</t>
+          <t>DPT464267</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER CREAM STRAWBERRY PUMP/250ML</t>
+          <t>DEEDEE TRAVEL PACK MIX</t>
         </is>
       </c>
       <c r="E131" s="3" t="n">
@@ -76732,22 +76732,22 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650264B</t>
+          <t>JIYDPT464267-Z0</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650264B</t>
+          <t>JIYDPT464267-Z0</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>DSC650264B</t>
+          <t>DPT464267-Z01</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER FOAMING STRAWBERRY PUMP/225ML</t>
+          <t>DEE-DEE TRAVEL PACK MIX+FREE GIFT-DPT464267Z0</t>
         </is>
       </c>
       <c r="E132" s="3" t="n">
@@ -76757,47 +76757,47 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650281</t>
+          <t>JIYDSC650264</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650281</t>
+          <t>JIYDSC650264</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>DSC650281</t>
+          <t>DSC650264</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER CREAM APPLE PUMP/250ML</t>
+          <t>DEEDEE SHOWER CREAM STRAWBERRY PUMP/250ML</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650281B</t>
+          <t>JIYDSC650264B</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650281B</t>
+          <t>JIYDSC650264B</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>DSC650281B</t>
+          <t>DSC650264B</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER FOAMING APPLE PUMP/225ML</t>
+          <t>DEEDEE SHOWER FOAMING STRAWBERRY PUMP/225ML</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
@@ -76807,22 +76807,22 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650282</t>
+          <t>JIYDSC650281</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650282</t>
+          <t>JIYDSC650281</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>DSC650282</t>
+          <t>DSC650281</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER CREAM GRAPE PUMP/250ML</t>
+          <t>DEEDEE SHOWER CREAM APPLE PUMP/250ML</t>
         </is>
       </c>
       <c r="E135" s="3" t="n">
@@ -76832,22 +76832,22 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650282B</t>
+          <t>JIYDSC650281B</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650282B</t>
+          <t>JIYDSC650281B</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>DSC650282B</t>
+          <t>DSC650281B</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER FOAMING GRAPE PUMP/225ML</t>
+          <t>DEEDEE SHOWER FOAMING APPLE PUMP/225ML</t>
         </is>
       </c>
       <c r="E136" s="3" t="n">
@@ -76857,47 +76857,47 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650283</t>
+          <t>JIYDSC650282</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650283</t>
+          <t>JIYDSC650282</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>DSC650283</t>
+          <t>DSC650282</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER CREAM ORANGE PUMP/250ML</t>
+          <t>DEEDEE SHOWER CREAM GRAPE PUMP/250ML</t>
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650283B</t>
+          <t>JIYDSC650282B</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC650283B</t>
+          <t>JIYDSC650282B</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>DSC650283B</t>
+          <t>DSC650282B</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER FOAMING ORANGE PUMP/225ML</t>
+          <t>DEEDEE SHOWER FOAMING GRAPE PUMP/225ML</t>
         </is>
       </c>
       <c r="E138" s="3" t="n">
@@ -76907,22 +76907,22 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC660291</t>
+          <t>JIYDSC650283</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC660291</t>
+          <t>JIYDSC650283</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>DSC660291</t>
+          <t>DSC650283</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER FOAMING APPLE /200ML</t>
+          <t>DEEDEE SHOWER CREAM ORANGE PUMP/250ML</t>
         </is>
       </c>
       <c r="E139" s="3" t="n">
@@ -76932,72 +76932,72 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC660292</t>
+          <t>JIYDSC650283B</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC660292</t>
+          <t>JIYDSC650283B</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>DSC660292</t>
+          <t>DSC650283B</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER FOAMING GRAPE /200ML</t>
+          <t>DEEDEE SHOWER FOAMING ORANGE PUMP/225ML</t>
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC660293</t>
+          <t>JIYDSC660291</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC660293</t>
+          <t>JIYDSC660291</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>DSC660293</t>
+          <t>DSC660291</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER FOAMING ORANGE /200ML</t>
+          <t>DEEDEE SHOWER FOAMING APPLE /200ML</t>
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC660294</t>
+          <t>JIYDSC660292</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>JIYDSC660294</t>
+          <t>JIYDSC660292</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>DSC660294</t>
+          <t>DSC660292</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE SHOWER FOAMING STRAWBERRY /200ML</t>
+          <t>DEEDEE SHOWER FOAMING GRAPE /200ML</t>
         </is>
       </c>
       <c r="E142" s="3" t="n">
@@ -77007,72 +77007,72 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>JIYDSG442482</t>
+          <t>JIYDSC660293</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>JIYDSG442482</t>
+          <t>JIYDSC660293</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>DSG442482</t>
+          <t>DSC660293</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE TOOTH BRUSH MIX /HANGER</t>
+          <t>DEEDEE SHOWER FOAMING ORANGE /200ML</t>
         </is>
       </c>
       <c r="E143" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>JIYDSG442492</t>
+          <t>JIYDSC660294</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>JIYDSG442492</t>
+          <t>JIYDSC660294</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>DSG442492</t>
+          <t>DSC660294</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE TOOTH BRUSH MIX /TRAY</t>
+          <t>DEEDEE SHOWER FOAMING STRAWBERRY /200ML</t>
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>JIYDSG442540</t>
+          <t>JIYDSG442482</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>JIYDSG442540</t>
+          <t>JIYDSG442482</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>DSG442540</t>
+          <t>DSG442482</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE TOOTH BRUSH PREMIUM BOX BESAR</t>
+          <t>DEEDEE TOOTH BRUSH MIX /HANGER</t>
         </is>
       </c>
       <c r="E145" s="3" t="n">
@@ -77082,247 +77082,247 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464191</t>
+          <t>JIYDSG442492</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464191</t>
+          <t>JIYDSG442492</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>DTP464191</t>
+          <t>DSG442492</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE TALCUM POWDER APPLE /45GR</t>
+          <t>DEEDEE TOOTH BRUSH MIX /TRAY</t>
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464193</t>
+          <t>JIYDSG442540</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464193</t>
+          <t>JIYDSG442540</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>DTP464193</t>
+          <t>DSG442540</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE TALCUM POWDER ORANGE /45GR</t>
+          <t>DEE DEE TOOTH BRUSH PREMIUM BOX BESAR</t>
         </is>
       </c>
       <c r="E147" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464194</t>
+          <t>JIYDTP464191</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464194</t>
+          <t>JIYDTP464191</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>DTP464194</t>
+          <t>DTP464191</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>DEEDEE TALCUM POWDER STRAWBERRY /45GR</t>
+          <t>DEEDEE TALCUM POWDER APPLE /45GR</t>
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464291</t>
+          <t>JIYDTP464193</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464291</t>
+          <t>JIYDTP464193</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>DTP464291</t>
+          <t>DTP464193</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE TALCUM POWDER - APPLE BTL/ 150GR + FREE FOAM STIKER CAR</t>
+          <t>DEEDEE TALCUM POWDER ORANGE /45GR</t>
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464291-Z0</t>
+          <t>JIYDTP464194</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464291-Z0</t>
+          <t>JIYDTP464194</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>DTP464291-Z01</t>
+          <t>DTP464194</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>DEE-DEE TALC PWD  APPLE 150GR FF S.CAR-DTP464291-Z</t>
+          <t>DEEDEE TALCUM POWDER STRAWBERRY /45GR</t>
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464293</t>
+          <t>JIYDTP464291</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464293</t>
+          <t>JIYDTP464291</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>DTP464293</t>
+          <t>DTP464291</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE TALCUM POWDER - ORANGE BTL/ 150GR + FREE FOAM STIKER CAR</t>
+          <t>DEE DEE TALCUM POWDER - APPLE BTL/ 150GR + FREE FOAM STIKER CAR</t>
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464294</t>
+          <t>JIYDTP464291-Z0</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>JIYDTP464294</t>
+          <t>JIYDTP464291-Z0</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>DTP464294</t>
+          <t>DTP464291-Z01</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>DEE DEE TALCUM POWDER - STRAWBERRY BTL/ 150GR + FREE FOAM STIKER CAR</t>
+          <t>DEE-DEE TALC PWD  APPLE 150GR FF S.CAR-DTP464291-Z</t>
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871393</t>
+          <t>JIYDTP464293</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871393</t>
+          <t>JIYDTP464293</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>ESC871393</t>
+          <t>DTP464293</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>EVANY SHOWERCREAM GREEN TEA /700ML</t>
+          <t>DEE DEE TALCUM POWDER - ORANGE BTL/ 150GR + FREE FOAM STIKER CAR</t>
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871394</t>
+          <t>JIYDTP464294</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871394</t>
+          <t>JIYDTP464294</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>ESC871394</t>
+          <t>DTP464294</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>EVANY SHOWERCREAM ROSE /700ML</t>
+          <t>DEE DEE TALCUM POWDER - STRAWBERRY BTL/ 150GR + FREE FOAM STIKER CAR</t>
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871395</t>
+          <t>JIYESC871393</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871395</t>
+          <t>JIYESC871393</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>ESC871395</t>
+          <t>ESC871393</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>EVANY SHOWERCREAM LAVENDER /700ML</t>
+          <t>EVANY SHOWERCREAM GREEN TEA /700ML</t>
         </is>
       </c>
       <c r="E155" s="3" t="n">
@@ -77332,22 +77332,22 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871396</t>
+          <t>JIYESC871394</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871396</t>
+          <t>JIYESC871394</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>ESC871396</t>
+          <t>ESC871394</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>EVANY SHOWERCREAM MILK /700ML</t>
+          <t>EVANY SHOWERCREAM ROSE /700ML</t>
         </is>
       </c>
       <c r="E156" s="3" t="n">
@@ -77357,22 +77357,22 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871993</t>
+          <t>JIYESC871395</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871993</t>
+          <t>JIYESC871395</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>ESC871993</t>
+          <t>ESC871395</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>EVANY SHOWERCREAM GREEN TEA /500ML</t>
+          <t>EVANY SHOWERCREAM LAVENDER /700ML</t>
         </is>
       </c>
       <c r="E157" s="3" t="n">
@@ -77382,22 +77382,22 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871994</t>
+          <t>JIYESC871396</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871994</t>
+          <t>JIYESC871396</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>ESC871994</t>
+          <t>ESC871396</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>EVANY SHOWERCREAM ROSE /500ML</t>
+          <t>EVANY SHOWERCREAM MILK /700ML</t>
         </is>
       </c>
       <c r="E158" s="3" t="n">
@@ -77407,22 +77407,22 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871995</t>
+          <t>JIYESC871993</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871995</t>
+          <t>JIYESC871993</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>ESC871995</t>
+          <t>ESC871993</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>EVANY SHOWERCREAM LAVENDER /500ML</t>
+          <t>EVANY SHOWERCREAM GREEN TEA /500ML</t>
         </is>
       </c>
       <c r="E159" s="3" t="n">
@@ -77432,22 +77432,22 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871996</t>
+          <t>JIYESC871994</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>JIYESC871996</t>
+          <t>JIYESC871994</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>ESC871996</t>
+          <t>ESC871994</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>EVANY SHOWERCREAM MILK /500ML</t>
+          <t>EVANY SHOWERCREAM ROSE /500ML</t>
         </is>
       </c>
       <c r="E160" s="3" t="n">
@@ -77457,22 +77457,22 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>JIYETB871267</t>
+          <t>JIYESC871995</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>JIYETB871267</t>
+          <t>JIYESC871995</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>ETB871267</t>
+          <t>ESC871995</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>EVANY PAKETMIX</t>
+          <t>EVANY SHOWERCREAM LAVENDER /500ML</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
@@ -77482,22 +77482,22 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178273</t>
+          <t>JIYESC871996</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178273</t>
+          <t>JIYESC871996</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>GLA178273</t>
+          <t>ESC871996</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>YURI GLASS CLEANER FOAMING FRESH LILAC 500ML P +500ML R</t>
+          <t>EVANY SHOWERCREAM MILK /500ML</t>
         </is>
       </c>
       <c r="E162" s="3" t="n">
@@ -77507,47 +77507,47 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178280</t>
+          <t>JIYETB871267</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178280</t>
+          <t>JIYETB871267</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>GLA178280</t>
+          <t>ETB871267</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>YURI GLASS CLEANER FOAMING FRESH BLUE SPRAY/500ML</t>
+          <t>EVANY PAKETMIX</t>
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178280-Z01</t>
+          <t>JIYGLA178273</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178280-Z01</t>
+          <t>JIYGLA178273</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>GLA178280-Z01</t>
+          <t>GLA178273</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>YURI GLASS CLEANER FOAMING FRESH BLUE SPRAY/500ML</t>
+          <t>YURI GLASS CLEANER FOAMING FRESH LILAC 500ML P +500ML R</t>
         </is>
       </c>
       <c r="E164" s="3" t="n">
@@ -77557,47 +77557,47 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178282</t>
+          <t>JIYGLA178280</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178282</t>
+          <t>JIYGLA178280</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>GLA178282</t>
+          <t>GLA178280</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>YURI GLASS CLEANER FOAMING LEMON SPRAY/500ML</t>
+          <t>YURI GLASS CLEANER FOAMING FRESH BLUE SPRAY/500ML</t>
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178282-Z01</t>
+          <t>JIYGLA178280-Z01</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178282-Z01</t>
+          <t>JIYGLA178280-Z01</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>GLA178282-Z01</t>
+          <t>GLA178280-Z01</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>YURI GC LEMONFRESH 500ML BTLSPR-FREE GCPOUCH 410ML</t>
+          <t>YURI GLASS CLEANER FOAMING FRESH BLUE SPRAY/500ML</t>
         </is>
       </c>
       <c r="E166" s="3" t="n">
@@ -77607,22 +77607,22 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178283</t>
+          <t>JIYGLA178282</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178283</t>
+          <t>JIYGLA178282</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>GLA178283</t>
+          <t>GLA178282</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>YURI GLASS CLEANER FOAMING FRESH LILAC SPRAY/500ML</t>
+          <t>YURI GLASS CLEANER FOAMING LEMON SPRAY/500ML</t>
         </is>
       </c>
       <c r="E167" s="3" t="n">
@@ -77632,22 +77632,22 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178283-Z01</t>
+          <t>JIYGLA178282-Z01</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178283-Z01</t>
+          <t>JIYGLA178282-Z01</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>GLA178283-Z01</t>
+          <t>GLA178282-Z01</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>YURI GC FRESLILAC 500ML BTL SPR-FREE GCPOUCH 410ML</t>
+          <t>YURI GC LEMONFRESH 500ML BTLSPR-FREE GCPOUCH 410ML</t>
         </is>
       </c>
       <c r="E168" s="3" t="n">
@@ -77657,22 +77657,22 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178590</t>
+          <t>JIYGLA178283</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178590</t>
+          <t>JIYGLA178283</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>GLA178590</t>
+          <t>GLA178283</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>YURI GLASS CLEANER FOAMING FRESH BLUE /3,7LT</t>
+          <t>YURI GLASS CLEANER FOAMING FRESH LILAC SPRAY/500ML</t>
         </is>
       </c>
       <c r="E169" s="3" t="n">
@@ -77682,97 +77682,97 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178592</t>
+          <t>JIYGLA178283-Z01</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178592</t>
+          <t>JIYGLA178283-Z01</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>GLA178592</t>
+          <t>GLA178283-Z01</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>YURI GLASS CLEANER FOAMING LEMON FRESH /3,7LT</t>
+          <t>YURI GC FRESLILAC 500ML BTL SPR-FREE GCPOUCH 410ML</t>
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178593</t>
+          <t>JIYGLA178590</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178593</t>
+          <t>JIYGLA178590</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>GLA178593</t>
+          <t>GLA178590</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>YURI GLASS CLEANER FOAMING FRESH LILAC /3,7LT</t>
+          <t>YURI GLASS CLEANER FOAMING FRESH BLUE /3,7LT</t>
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178990</t>
+          <t>JIYGLA178592</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178990</t>
+          <t>JIYGLA178592</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>GLA178990</t>
+          <t>GLA178592</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>YURI GLASS CLEANER FOAMING FRESH BLUE /410ML</t>
+          <t>YURI GLASS CLEANER FOAMING LEMON FRESH /3,7LT</t>
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178990-Z0</t>
+          <t>JIYGLA178593</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178990-Z0</t>
+          <t>JIYGLA178593</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>GLA178990-Z01</t>
+          <t>GLA178593</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>GLASS CLEANER FRESH BLUE-POUCH/410ML B1G1</t>
+          <t>YURI GLASS CLEANER FOAMING FRESH LILAC /3,7LT</t>
         </is>
       </c>
       <c r="E173" s="3" t="n">
@@ -77782,22 +77782,22 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178992</t>
+          <t>JIYGLA178990</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178992</t>
+          <t>JIYGLA178990</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>GLA178992</t>
+          <t>GLA178990</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>YURI GLASS CLEANER FOAMING LEMON FRESH /410ML</t>
+          <t>YURI GLASS CLEANER FOAMING FRESH BLUE /410ML</t>
         </is>
       </c>
       <c r="E174" s="3" t="n">
@@ -77807,22 +77807,22 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178992-Z0</t>
+          <t>JIYGLA178990-Z0</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178992-Z0</t>
+          <t>JIYGLA178990-Z0</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>GLA178992-Z01</t>
+          <t>GLA178990-Z01</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>GLASS CLEANER LEMON FRESH -POUCH/410ML B1G1</t>
+          <t>GLASS CLEANER FRESH BLUE-POUCH/410ML B1G1</t>
         </is>
       </c>
       <c r="E175" s="3" t="n">
@@ -77832,22 +77832,22 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178993</t>
+          <t>JIYGLA178992</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178993</t>
+          <t>JIYGLA178992</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>GLA178993</t>
+          <t>GLA178992</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>YURI GLASS CLEANER FOAMING LILAC  /410ML</t>
+          <t>YURI GLASS CLEANER FOAMING LEMON FRESH /410ML</t>
         </is>
       </c>
       <c r="E176" s="3" t="n">
@@ -77857,22 +77857,22 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178993-Z0</t>
+          <t>JIYGLA178992-Z0</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>JIYGLA178993-Z0</t>
+          <t>JIYGLA178992-Z0</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>GLA178993-Z01</t>
+          <t>GLA178992-Z01</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>GLASS CLEANER FRESH LILAC-POUCH/410ML B1G1</t>
+          <t>GLASS CLEANER LEMON FRESH -POUCH/410ML B1G1</t>
         </is>
       </c>
       <c r="E177" s="3" t="n">
@@ -77882,122 +77882,122 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>JIYHSA981283A</t>
+          <t>JIYGLA178993</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>JIYHSA981283A</t>
+          <t>JIYGLA178993</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>HSA981283A</t>
+          <t>GLA178993</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP FOAMING GREEN TEA /410ML</t>
+          <t>YURI GLASS CLEANER FOAMING LILAC  /410ML</t>
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>JIYHSA981284A</t>
+          <t>JIYGLA178993-Z0</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>JIYHSA981284A</t>
+          <t>JIYGLA178993-Z0</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>HSA981284A</t>
+          <t>GLA178993-Z01</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP FOAMING ROSE /410ML</t>
+          <t>GLASS CLEANER FRESH LILAC-POUCH/410ML B1G1</t>
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>JIYHSA981993A</t>
+          <t>JIYHSA981283A</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>JIYHSA981993A</t>
+          <t>JIYHSA981283A</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>HSA981993A</t>
+          <t>HSA981283A</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP FOAMING GREEN TEA /375ML</t>
+          <t>YURI HAND SOAP FOAMING GREEN TEA /410ML</t>
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>JIYHSA981994A</t>
+          <t>JIYHSA981284A</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>JIYHSA981994A</t>
+          <t>JIYHSA981284A</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>HSA981994A</t>
+          <t>HSA981284A</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP FOAMING ROSE /375ML</t>
+          <t>YURI HAND SOAP FOAMING ROSE /410ML</t>
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>JIYHSA981995A</t>
+          <t>JIYHSA981993A</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>JIYHSA981995A</t>
+          <t>JIYHSA981993A</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>HSA981995A</t>
+          <t>HSA981993A</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP FOAMING LAVANDER /375ML</t>
+          <t>YURI HAND SOAP FOAMING GREEN TEA /375ML</t>
         </is>
       </c>
       <c r="E182" s="3" t="n">
@@ -78007,197 +78007,197 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222381</t>
+          <t>JIYHSA981994A</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222381</t>
+          <t>JIYHSA981994A</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>HSP222381</t>
+          <t>HSA981994A</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP APPLE PUMP /410ML</t>
+          <t>YURI HAND SOAP FOAMING ROSE /375ML</t>
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222383</t>
+          <t>JIYHSA981995A</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222383</t>
+          <t>JIYHSA981995A</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>HSP222383</t>
+          <t>HSA981995A</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP GRAPES PUMP /410ML</t>
+          <t>YURI HAND SOAP FOAMING LAVANDER /375ML</t>
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222384</t>
+          <t>JIYHSP222381</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222384</t>
+          <t>JIYHSP222381</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>HSP222384</t>
+          <t>HSP222381</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP LEMON PUMP /410ML</t>
+          <t>YURI HAND SOAP APPLE PUMP /410ML</t>
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222385</t>
+          <t>JIYHSP222383</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222385</t>
+          <t>JIYHSP222383</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>HSP222385</t>
+          <t>HSP222383</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP ORANGE PUMP /410ML</t>
+          <t>YURI HAND SOAP GRAPES PUMP /410ML</t>
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222386</t>
+          <t>JIYHSP222384</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222386</t>
+          <t>JIYHSP222384</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>HSP222386</t>
+          <t>HSP222384</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP STRAWBERRY PUMP /410ML</t>
+          <t>YURI HAND SOAP LEMON PUMP /410ML</t>
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222791</t>
+          <t>JIYHSP222385</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222791</t>
+          <t>JIYHSP222385</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>HSP222791</t>
+          <t>HSP222385</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP APPLE 375ML + 410ML PUMP</t>
+          <t>YURI HAND SOAP ORANGE PUMP /410ML</t>
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222793</t>
+          <t>JIYHSP222386</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222793</t>
+          <t>JIYHSP222386</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>HSP222793</t>
+          <t>HSP222386</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP GRAPE 375ML + 410ML PUMP</t>
+          <t>YURI HAND SOAP STRAWBERRY PUMP /410ML</t>
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222794</t>
+          <t>JIYHSP222791</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222794</t>
+          <t>JIYHSP222791</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>HSP222794</t>
+          <t>HSP222791</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP LEMON 375ML + 410ML PUMP</t>
+          <t>YURI HAND SOAP APPLE 375ML + 410ML PUMP</t>
         </is>
       </c>
       <c r="E190" s="3" t="n">
@@ -78207,22 +78207,22 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222795</t>
+          <t>JIYHSP222793</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222795</t>
+          <t>JIYHSP222793</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>HSP222795</t>
+          <t>HSP222793</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP ORANGE 375ML + 410ML PUMP</t>
+          <t>YURI HAND SOAP GRAPE 375ML + 410ML PUMP</t>
         </is>
       </c>
       <c r="E191" s="3" t="n">
@@ -78232,22 +78232,22 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222796</t>
+          <t>JIYHSP222794</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP222796</t>
+          <t>JIYHSP222794</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>HSP222796</t>
+          <t>HSP222794</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP STRAWBERRY 375ML + 410ML PUMP</t>
+          <t>YURI HAND SOAP LEMON 375ML + 410ML PUMP</t>
         </is>
       </c>
       <c r="E192" s="3" t="n">
@@ -78257,47 +78257,47 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP223301</t>
+          <t>JIYHSP222795</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP223301</t>
+          <t>JIYHSP222795</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>HSP223301</t>
+          <t>HSP222795</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP LAVENDER  PUMP/410ML</t>
+          <t>YURI HAND SOAP ORANGE 375ML + 410ML PUMP</t>
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP22331A</t>
+          <t>JIYHSP222796</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>JIYHSP22331A</t>
+          <t>JIYHSP222796</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>HSA981385</t>
+          <t>HSP222796</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>YURI HANDSOAP FOAMING  LAVENDER 410ML +HS 375ML</t>
+          <t>YURI HAND SOAP STRAWBERRY 375ML + 410ML PUMP</t>
         </is>
       </c>
       <c r="E194" s="3" t="n">
@@ -78307,97 +78307,97 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222591</t>
+          <t>JIYHSP223301</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222591</t>
+          <t>JIYHSP223301</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>HSR222591</t>
+          <t>HSP223301</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP APPLE  /3,7LT</t>
+          <t>YURI HAND SOAP LAVENDER  PUMP/410ML</t>
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222593</t>
+          <t>JIYHSP22331A</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222593</t>
+          <t>JIYHSP22331A</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>HSR222593</t>
+          <t>HSA981385</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP GRAPE  /3,7LT</t>
+          <t>YURI HANDSOAP FOAMING  LAVENDER 410ML +HS 375ML</t>
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222594</t>
+          <t>JIYHSR222591</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222594</t>
+          <t>JIYHSR222591</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>HSR222594</t>
+          <t>HSR222591</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP LEMON  /3,7LT</t>
+          <t>YURI HAND SOAP APPLE  /3,7LT</t>
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222595</t>
+          <t>JIYHSR222593</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222595</t>
+          <t>JIYHSR222593</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>HSR222595</t>
+          <t>HSR222593</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP ORANGE  /3,7LT</t>
+          <t>YURI HAND SOAP GRAPE  /3,7LT</t>
         </is>
       </c>
       <c r="E198" s="3" t="n">
@@ -78407,347 +78407,347 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222596</t>
+          <t>JIYHSR222595</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222596</t>
+          <t>JIYHSR222595</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>HSR222596</t>
+          <t>HSR222595</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP STRAWBERRY  /3,7LT</t>
+          <t>YURI HAND SOAP ORANGE  /3,7LT</t>
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222991</t>
+          <t>JIYHSR222596</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222991</t>
+          <t>JIYHSR222596</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>HSR222991</t>
+          <t>HSR222596</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP APPLE  /375ML</t>
+          <t>YURI HAND SOAP STRAWBERRY  /3,7LT</t>
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222991-Z0</t>
+          <t>JIYHSR222991</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222991-Z0</t>
+          <t>JIYHSR222991</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>HSR222991-Z01</t>
+          <t>HSR222991</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>YURI H SOAP APPLE 375ML+BUY 1 GET 1-HSR222991Z0</t>
+          <t>YURI HAND SOAP APPLE  /375ML</t>
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222993</t>
+          <t>JIYHSR222991-Z0</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222993</t>
+          <t>JIYHSR222991-Z0</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>HSR222993</t>
+          <t>HSR222991-Z01</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP GRAPE  /375ML</t>
+          <t>YURI H SOAP APPLE 375ML+BUY 1 GET 1-HSR222991Z0</t>
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222993-Z0</t>
+          <t>JIYHSR222993</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222993-Z0</t>
+          <t>JIYHSR222993</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>HSR222993-Z01</t>
+          <t>HSR222993</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>YURI H SOAP GRAPE 375ML+BUY 1 GET 1-HSR222993Z0</t>
+          <t>YURI HAND SOAP GRAPE  /375ML</t>
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222994</t>
+          <t>JIYHSR222993-Z0</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222994</t>
+          <t>JIYHSR222993-Z0</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>HSR222994</t>
+          <t>HSR222993-Z01</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP LEMON  /375ML</t>
+          <t>YURI H SOAP GRAPE 375ML+BUY 1 GET 1-HSR222993Z0</t>
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222994-Z0</t>
+          <t>JIYHSR222994</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222994-Z0</t>
+          <t>JIYHSR222994</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>HSR222994-Z01</t>
+          <t>HSR222994</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>YURI H SOAP LEMON 375ML+BUY 1 GET 1-HSR222994Z0</t>
+          <t>YURI HAND SOAP LEMON  /375ML</t>
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222995</t>
+          <t>JIYHSR222994-Z0</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222995</t>
+          <t>JIYHSR222994-Z0</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>HSR222995</t>
+          <t>HSR222994-Z01</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP ORANGE  /375ML</t>
+          <t>YURI H SOAP LEMON 375ML+BUY 1 GET 1-HSR222994Z0</t>
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222995-Z0</t>
+          <t>JIYHSR222995</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222995-Z0</t>
+          <t>JIYHSR222995</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>HSR222995-Z01</t>
+          <t>HSR222995</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>YURI H SOAP ORANGE 375ML+BUY 1 GET 1-HSR222995Z0</t>
+          <t>YURI HAND SOAP ORANGE  /375ML</t>
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222996</t>
+          <t>JIYHSR222995-Z0</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222996</t>
+          <t>JIYHSR222995-Z0</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>HSR222996</t>
+          <t>HSR222995-Z01</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>YURI HAND SOAP STRAW  /375ML</t>
+          <t>YURI H SOAP ORANGE 375ML+BUY 1 GET 1-HSR222995Z0</t>
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222996-Z0</t>
+          <t>JIYHSR222996</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>JIYHSR222996-Z0</t>
+          <t>JIYHSR222996</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>HSR222996-Z01</t>
+          <t>HSR222996</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>YURI H SOAP STRWBERY 375ML+BUY 1 GET 1-HSR222996Z0</t>
+          <t>YURI HAND SOAP STRAW  /375ML</t>
         </is>
       </c>
       <c r="E209" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>JIYLIB257381</t>
+          <t>JIYHSR222996-Z0</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>JIYLIB257381</t>
+          <t>JIYHSR222996-Z0</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>LIB257381</t>
+          <t>HSR222996-Z01</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>LIGENT BABY PUMP /450ML FREE GIFT</t>
+          <t>YURI H SOAP STRWBERY 375ML+BUY 1 GET 1-HSR222996Z0</t>
         </is>
       </c>
       <c r="E210" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>JIYLIB257991</t>
+          <t>JIYLIB257381</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>JIYLIB257991</t>
+          <t>JIYLIB257381</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>LIB257991</t>
+          <t>LIB257381</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>LIGENT BABY POUCH /410ML</t>
+          <t>LIGENT BABY PUMP /450ML FREE GIFT</t>
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>JIYLIG252111</t>
+          <t>JIYLIB257991</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>JIYLIG252111</t>
+          <t>JIYLIB257991</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>LIG252111</t>
+          <t>LIB257991</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>LIGENT LIME  /80ML</t>
+          <t>LIGENT BABY POUCH /410ML</t>
         </is>
       </c>
       <c r="E212" s="3" t="n">
@@ -78757,22 +78757,22 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>JIYLIG252112</t>
+          <t>JIYLIG252111</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>JIYLIG252112</t>
+          <t>JIYLIG252111</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>LIG252112</t>
+          <t>LIG252111</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>LIGENT LEMON  /80ML</t>
+          <t>LIGENT LIME  /80ML</t>
         </is>
       </c>
       <c r="E213" s="3" t="n">
@@ -78782,22 +78782,22 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>JIYLIG252115</t>
+          <t>JIYLIG252112</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>JIYLIG252115</t>
+          <t>JIYLIG252112</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>LIG252115</t>
+          <t>LIG252112</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>LIGENT GRAPEFRUIT  /80ML</t>
+          <t>LIGENT LEMON  /80ML</t>
         </is>
       </c>
       <c r="E214" s="3" t="n">
@@ -78807,22 +78807,22 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>JIYLIG252451A</t>
+          <t>JIYLIG252115</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>JIYLIG252451A</t>
+          <t>JIYLIG252115</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>LIG252451A</t>
+          <t>LIG252115</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>LIGENT LIME PUMP 1L + GLASS CLEANER 500 ML SPRAY</t>
+          <t>LIGENT GRAPEFRUIT  /80ML</t>
         </is>
       </c>
       <c r="E215" s="3" t="n">
@@ -78832,22 +78832,22 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>JIYLIG252452A</t>
+          <t>JIYLIG252451A</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>JIYLIG252452A</t>
+          <t>JIYLIG252451A</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>LIG252452A</t>
+          <t>LIG252451A</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>LIGENT LEMON PUMP 1L + GLASS CLEANER 500 ML SPRAY</t>
+          <t>LIGENT LIME PUMP 1L + GLASS CLEANER 500 ML SPRAY</t>
         </is>
       </c>
       <c r="E216" s="3" t="n">
@@ -78857,22 +78857,22 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211943</t>
+          <t>JIYLIG252452A</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211943</t>
+          <t>JIYLIG252452A</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>MAT211943</t>
+          <t>LIG252452A</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC LOW SUDS  /1.8KG</t>
+          <t>LIGENT LEMON PUMP 1L + GLASS CLEANER 500 ML SPRAY</t>
         </is>
       </c>
       <c r="E217" s="3" t="n">
@@ -79832,72 +79832,72 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211191</t>
+          <t>JIYMAT211391</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211191</t>
+          <t>JIYMAT211391</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>MAT211191</t>
+          <t>MAT211391</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC TOUGH STAIN  /80ML</t>
+          <t>YURIMATIC TOUGH STAIN  /1KG</t>
         </is>
       </c>
       <c r="E256" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211391</t>
+          <t>JIYMAT211392</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211391</t>
+          <t>JIYMAT211392</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>MAT211391</t>
+          <t>MAT211392</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC TOUGH STAIN  /1KG</t>
+          <t>YURIMATIC COLOUR  /1KG</t>
         </is>
       </c>
       <c r="E257" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211392</t>
+          <t>JIYMAT211393</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211392</t>
+          <t>JIYMAT211393</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>MAT211392</t>
+          <t>MAT211393</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC COLOUR  /1KG</t>
+          <t>YURIMATIC LOW SUDS  /1KG</t>
         </is>
       </c>
       <c r="E258" s="3" t="n">
@@ -79907,22 +79907,22 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211393</t>
+          <t>JIYMAT211451A</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211393</t>
+          <t>JIYMAT211451A</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>MAT211393</t>
+          <t>MAT211451A</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC LOW SUDS  /1KG</t>
+          <t>YUTIMATIC 1.8KG T STAINS + TRIL SPRAY 500ML</t>
         </is>
       </c>
       <c r="E259" s="3" t="n">
@@ -79932,22 +79932,22 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211451A</t>
+          <t>JIYMAT211452A</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211451A</t>
+          <t>JIYMAT211452A</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>MAT211451A</t>
+          <t>MAT211452A</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>YUTIMATIC 1.8KG T STAINS + TRIL SPRAY 500ML</t>
+          <t>YUTIMATIC 1.8KG COLOUR + TRIL SPRAY 500ML</t>
         </is>
       </c>
       <c r="E260" s="3" t="n">
@@ -79957,22 +79957,22 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211452A</t>
+          <t>JIYMAT211453A</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211452A</t>
+          <t>JIYMAT211453A</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>MAT211452A</t>
+          <t>MAT211453A</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>YUTIMATIC 1.8KG COLOUR + TRIL SPRAY 500ML</t>
+          <t>YUTIMATIC 1.8KG LOW SUD + TRIL SPRAY 500ML</t>
         </is>
       </c>
       <c r="E261" s="3" t="n">
@@ -79982,22 +79982,22 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211453A</t>
+          <t>JIYMAT211591</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211453A</t>
+          <t>JIYMAT211591</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>MAT211453A</t>
+          <t>MAT211591</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>YUTIMATIC 1.8KG LOW SUD + TRIL SPRAY 500ML</t>
+          <t>YURIMATIC TOUGH STAIN  /3,7LT</t>
         </is>
       </c>
       <c r="E262" s="3" t="n">
@@ -80007,22 +80007,22 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211591</t>
+          <t>JIYMAT211591-Z0</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211591</t>
+          <t>JIYMAT211591-Z0</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>MAT211591</t>
+          <t>MAT211591-Z01</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC TOUGH STAIN  /3,7LT</t>
+          <t>YURIMATIC TOUGH STAIN  /3,7LT + GRATIS HANDSOAP 375ML</t>
         </is>
       </c>
       <c r="E263" s="3" t="n">
@@ -80032,22 +80032,22 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211591-Z0</t>
+          <t>JIYMAT211592</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211591-Z0</t>
+          <t>JIYMAT211592</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>MAT211591-Z01</t>
+          <t>MAT211592</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC TOUGH STAIN  /3,7LT + GRATIS HANDSOAP 375ML</t>
+          <t>YURIMATIC COLOUR  /3,7LT</t>
         </is>
       </c>
       <c r="E264" s="3" t="n">
@@ -80057,22 +80057,22 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211592</t>
+          <t>JIYMAT211592-Z0</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211592</t>
+          <t>JIYMAT211592-Z0</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>MAT211592</t>
+          <t>MAT211592-Z01</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC COLOUR  /3,7LT</t>
+          <t>YURIMATIC COLOUR  /3,7LT + GRATIS HANDSOAP 375ML</t>
         </is>
       </c>
       <c r="E265" s="3" t="n">
@@ -80082,22 +80082,22 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211592-Z0</t>
+          <t>JIYMAT211593</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211592-Z0</t>
+          <t>JIYMAT211593</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>MAT211592-Z01</t>
+          <t>MAT211593</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC COLOUR  /3,7LT + GRATIS HANDSOAP 375ML</t>
+          <t>YURIMATIC LOW SUDS  /3,7LT</t>
         </is>
       </c>
       <c r="E266" s="3" t="n">
@@ -80107,22 +80107,22 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211593</t>
+          <t>JIYMAT211593-Z0</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211593</t>
+          <t>JIYMAT211593-Z0</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>MAT211593</t>
+          <t>MAT211593-Z01</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC LOW SUDS  /3,7LT</t>
+          <t>YURIMATIC LOW SUDS  /3,7LT + GRATIS HANDSOAP 375ML</t>
         </is>
       </c>
       <c r="E267" s="3" t="n">
@@ -80132,22 +80132,22 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211593-Z0</t>
+          <t>JIYMAT211751</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211593-Z0</t>
+          <t>JIYMAT211751</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>MAT211593-Z01</t>
+          <t>MAT211751</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC LOW SUDS  /3,7LT + GRATIS HANDSOAP 375ML</t>
+          <t>YURI MATIC TOUGH STAINS BUY2GET1 / 630G</t>
         </is>
       </c>
       <c r="E268" s="3" t="n">
@@ -80157,22 +80157,22 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211751</t>
+          <t>JIYMAT211752</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211751</t>
+          <t>JIYMAT211752</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>MAT211751</t>
+          <t>MAT211752</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>YURI MATIC TOUGH STAINS BUY2GET1 / 630G</t>
+          <t>YURI MATIC COLOUR BUY2GET1 / 630G</t>
         </is>
       </c>
       <c r="E269" s="3" t="n">
@@ -80182,22 +80182,22 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211752</t>
+          <t>JIYMAT211753</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211752</t>
+          <t>JIYMAT211753</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>MAT211752</t>
+          <t>MAT211753</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>YURI MATIC COLOUR BUY2GET1 / 630G</t>
+          <t>YURI MATIC LOWSUDS BUY2GET1 / 630G</t>
         </is>
       </c>
       <c r="E270" s="3" t="n">
@@ -80207,22 +80207,22 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211753</t>
+          <t>JIYMAT211932</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211753</t>
+          <t>JIYMAT211932</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>MAT211753</t>
+          <t>MAT211932</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>YURI MATIC LOWSUDS BUY2GET1 / 630G</t>
+          <t>YURIMATIC POUCH COLOUR 1.6 KG BUY 1 GET 1 FREE</t>
         </is>
       </c>
       <c r="E271" s="3" t="n">
@@ -80232,22 +80232,22 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211932</t>
+          <t>JIYMAT211933</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211932</t>
+          <t>JIYMAT211933</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>MAT211932</t>
+          <t>MAT211933</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC POUCH COLOUR 1.6 KG BUY 1 GET 1 FREE</t>
+          <t>YURIMATIC POUCH LOWSUDS 1.6 KG BUY 1 GET 1 FREE</t>
         </is>
       </c>
       <c r="E272" s="3" t="n">
@@ -80257,22 +80257,22 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211933</t>
+          <t>JIYMAT211941</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211933</t>
+          <t>JIYMAT211941</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>MAT211933</t>
+          <t>MAT211941</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC POUCH LOWSUDS 1.6 KG BUY 1 GET 1 FREE</t>
+          <t>YURIMATIC TOUGH STAIN  /1.8KG</t>
         </is>
       </c>
       <c r="E273" s="3" t="n">
@@ -80282,22 +80282,22 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211941</t>
+          <t>JIYMAT211942</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211941</t>
+          <t>JIYMAT211942</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>MAT211941</t>
+          <t>MAT211942</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC TOUGH STAIN  /1.8KG</t>
+          <t>YURIMATIC COLOUR  /1.8KG</t>
         </is>
       </c>
       <c r="E274" s="3" t="n">
@@ -80307,22 +80307,22 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211942</t>
+          <t>JIYMAT211943</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>JIYMAT211942</t>
+          <t>JIYMAT211943</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>MAT211942</t>
+          <t>MAT211943</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>YURIMATIC COLOUR  /1.8KG</t>
+          <t>YURIMATIC LOW SUDS  /1.8KG</t>
         </is>
       </c>
       <c r="E275" s="3" t="n">
